--- a/output/2026-10-06_05_Croazia_Grad_Zagreb_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-10-06_05_Croazia_Grad_Zagreb_Impiantistica_aspirazione_industriale.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,6 @@
           <t>+385 1 3818 004</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Sul mercato croato dal 1998, Premium Partner Filtration Group Industrial. Email aziendale non confermata con fonte certa, lasciata vuota.</t>
@@ -544,7 +543,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -586,7 +585,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -628,7 +627,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
